--- a/aec/results/신촌/logistic_results.xlsx
+++ b/aec/results/신촌/logistic_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -710,7 +710,7 @@
         <v>11.7509</v>
       </c>
       <c r="C2" t="n">
-        <v>126868.4674</v>
+        <v>126868.466</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
         <v>121.0235</v>
       </c>
       <c r="C21" t="n">
-        <v>3.629552230970935e+52</v>
+        <v>3.629551954709278e+52</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1304,7 +1304,7 @@
         <v>136.4841</v>
       </c>
       <c r="C35" t="n">
-        <v>1.880610302180746e+59</v>
+        <v>1.880610138473604e+59</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         <v>130.2981</v>
       </c>
       <c r="C47" t="n">
-        <v>3.870378678550905e+56</v>
+        <v>3.87037835553249e+56</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
         <v>120.0481</v>
       </c>
       <c r="C52" t="n">
-        <v>1.368410520058814e+52</v>
+        <v>1.368410416321512e+52</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -1628,7 +1628,7 @@
         <v>106.3247</v>
       </c>
       <c r="C53" t="n">
-        <v>1.500434572365682e+46</v>
+        <v>1.500434470303972e+46</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
         <v>205.8957</v>
       </c>
       <c r="C55" t="n">
-        <v>2.626468543852966e+89</v>
+        <v>2.626468207671853e+89</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>

--- a/aec/results/신촌/logistic_results.xlsx
+++ b/aec/results/신촌/logistic_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,19 +469,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.0756</v>
+        <v>1.0681</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8353</v>
+        <v>0.8275</v>
       </c>
       <c r="D2" t="n">
-        <v>1.385</v>
+        <v>1.3787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.572141</v>
+        <v>0.612907</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5091</v>
+        <v>0.5082</v>
       </c>
     </row>
     <row r="3">
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.4364</v>
+        <v>1.4412</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2482</v>
+        <v>1.2506</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6531</v>
+        <v>1.6609</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.614</v>
+        <v>0.6147</v>
       </c>
     </row>
     <row r="4">
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7019</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6036</v>
+        <v>0.6037</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8163</v>
+        <v>0.8188</v>
       </c>
       <c r="E4" t="n">
-        <v>4e-06</v>
+        <v>6e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.594</v>
+        <v>0.5944</v>
       </c>
     </row>
     <row r="5">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.1002</v>
+        <v>1.0964</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9718</v>
+        <v>0.9674</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2455</v>
+        <v>1.2425</v>
       </c>
       <c r="E5" t="n">
-        <v>0.131477</v>
+        <v>0.149725</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5356</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +557,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9912</v>
+        <v>0.9473</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8744</v>
+        <v>0.8349</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1236</v>
+        <v>1.0748</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8897350000000001</v>
+        <v>0.400678</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5157</v>
+        <v>0.5169</v>
       </c>
     </row>
     <row r="7">
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7514</v>
+        <v>0.722</v>
       </c>
       <c r="C7" t="n">
-        <v>0.53</v>
+        <v>0.5026</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0652</v>
+        <v>1.0371</v>
       </c>
       <c r="E7" t="n">
-        <v>0.108413</v>
+        <v>0.077919</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5533</v>
+        <v>0.5577</v>
       </c>
     </row>
     <row r="8">
@@ -601,19 +601,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6945</v>
+        <v>0.6937</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5991</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8051</v>
+        <v>0.8055</v>
       </c>
       <c r="E8" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5981</v>
+        <v>0.5988</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LR_χ²=70.594</t>
+          <t>LR_χ²=69.56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.011341</v>
+        <v>0.010866</v>
       </c>
       <c r="F9" t="n">
-        <v>0.602</v>
+        <v>0.6017</v>
       </c>
     </row>
   </sheetData>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.7509</v>
+        <v>8.9108</v>
       </c>
       <c r="C2" t="n">
-        <v>126868.466</v>
+        <v>7411.3487</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1551</v>
+        <v>0.1489</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1677</v>
+        <v>1.1606</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4235</v>
+        <v>0.4272</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5273</v>
+        <v>1.5329</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8444</v>
+        <v>0.9794</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3265</v>
+        <v>2.6629</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2678</v>
+        <v>0.3017</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3071</v>
+        <v>1.3522</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1134</v>
+        <v>-0.1432</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8928</v>
+        <v>0.8665</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5223</v>
+        <v>0.5446</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6859</v>
+        <v>1.724</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.6562</v>
+        <v>-1.7924</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1909</v>
+        <v>0.1666</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-94.7333</v>
+        <v>-81.6677</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-13.3437</v>
+        <v>-10.4092</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-48.0595</v>
+        <v>-39.9416</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-196.7057</v>
+        <v>-168.5773</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-13.5405</v>
+        <v>-10.7408</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-63.0547</v>
+        <v>-52.0151</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-32.213</v>
+        <v>-26.5489</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-12.3117</v>
+        <v>-9.401199999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-79.74550000000001</v>
+        <v>-69.7624</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-49.3882</v>
+        <v>-41.1846</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-12.1815</v>
+        <v>-9.972</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>121.0235</v>
+        <v>105.3565</v>
       </c>
       <c r="C21" t="n">
-        <v>3.629551954709278e+52</v>
+        <v>5.698362895386974e+45</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-62.5225</v>
+        <v>-49.4268</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-92.6157</v>
+        <v>-82.8691</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-17.0043</v>
+        <v>-17.2414</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-91.3698</v>
+        <v>-77.714</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-11.2473</v>
+        <v>-8.3691</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-72.9802</v>
+        <v>-62.3162</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-13.3397</v>
+        <v>-10.5004</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-12.3941</v>
+        <v>-9.369</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -1207,11 +1207,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-24.8986</v>
+        <v>-25.0115</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1225,11 +1225,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-29.0098</v>
+        <v>-150.7856</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1243,14 +1243,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-189.6884</v>
+        <v>-9.6699</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -1261,14 +1261,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-12.565</v>
+        <v>-8.9626</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -1279,14 +1279,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-11.8201</v>
+        <v>117.6051</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1.189168026865881e+51</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -1297,14 +1297,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>136.4841</v>
+        <v>-46.0376</v>
       </c>
       <c r="C35" t="n">
-        <v>1.880610138473604e+59</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -1315,11 +1315,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-52.6682</v>
+        <v>-43.812</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1333,11 +1333,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-52.4581</v>
+        <v>-60.6388</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -1351,11 +1351,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-68.2931</v>
+        <v>-10.0363</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1369,11 +1369,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-12.9269</v>
+        <v>-10.2901</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1387,11 +1387,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-13.1767</v>
+        <v>-10.3451</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1405,11 +1405,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-13.2283</v>
+        <v>-41.8123</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1423,11 +1423,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-47.8223</v>
+        <v>-45.6609</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1441,11 +1441,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-52.1735</v>
+        <v>-10.9442</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1459,11 +1459,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-13.7888</v>
+        <v>-9.9175</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1477,11 +1477,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-12.7478</v>
+        <v>-10.9757</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1495,14 +1495,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-13.7751</v>
+        <v>113.8601</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2.810777264241634e+49</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -1513,14 +1513,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>130.2981</v>
+        <v>-70.49550000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>3.87037835553249e+56</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -1531,11 +1531,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-80.0461</v>
+        <v>-29.0795</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1549,14 +1549,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-33.5737</v>
+        <v>-9.481999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -1567,11 +1567,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-12.3246</v>
+        <v>-11.3951</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -1585,14 +1585,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-14.2618</v>
+        <v>100.0617</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2.859289574977098e+43</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -1603,14 +1603,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>120.0481</v>
+        <v>84.91030000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>1.368410416321512e+52</v>
+        <v>7.517643574938535e+36</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -1621,14 +1621,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>106.3247</v>
+        <v>-10.3286</v>
       </c>
       <c r="C53" t="n">
-        <v>1.500434470303972e+46</v>
+        <v>0</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -1639,38 +1639,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-13.2114</v>
+        <v>176.5196</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>4.586562914514311e+76</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>205.8957</v>
-      </c>
-      <c r="C55" t="n">
-        <v>2.626468207671853e+89</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1710,7 +1692,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1725,7 +1707,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1740,7 +1722,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1755,7 +1737,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.718</v>
+        <v>0.7221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1770,7 +1752,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6868</v>
+        <v>0.6881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1785,7 +1767,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7494</v>
+        <v>0.7531</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1811,7 +1793,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2585</v>
+        <v>0.2496</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -1822,7 +1804,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.652</v>
+        <v>0.6975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1837,7 +1819,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1852,7 +1834,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3962</v>
+        <v>0.3953</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,7 +1849,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8562</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,7 +1864,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -1893,7 +1875,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>661</v>
+        <v>616</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -1904,7 +1886,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -1915,7 +1897,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -1926,7 +1908,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.283</v>
+        <v>6.3538</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1941,7 +1923,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.615564</v>
+        <v>0.607666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1969,7 +1951,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1713</v>
+        <v>0.1755</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1984,7 +1966,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.162</v>
+        <v>0.1625</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1999,7 +1981,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1396.34</v>
+        <v>1364.49</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2014,7 +1996,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1675.4</v>
+        <v>1637.06</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2029,7 +2011,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" t="inlineStr"/>
     </row>
